--- a/out/Attention-Mamba1_repeat_2_000001.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4867320633075707</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.4867320633075707</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>5.653970270522432</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>5.653970270522432</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>5.653970270522432</v>
+        <v>-0.4867320633075707</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0004499998998588417</v>
+        <v>-6.024599966383539e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1937568916215206</v>
+        <v>0.02594007120283165</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>5.653970270522432</v>
+        <v>-0.4867320633075707</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.3880308691591267</v>
+        <v>0.05194958456824068</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.7485845139206162</v>
+        <v>0.1002202135477871</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.06608343730067917</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.69194014772856</v>
+        <v>0.2265177186324669</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2302687928309839</v>
+        <v>0.03082880850472468</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.402944936957548</v>
+        <v>0.1878265949115294</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.04672325095406269</v>
+        <v>0.006254329953407621</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.265761806680401</v>
+        <v>0.1694594894501376</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.04046441184238865</v>
+        <v>0.005415387690751916</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.29991602913028</v>
+        <v>0.1740299889545944</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01978213259579021</v>
+        <v>0.002644567099335561</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.29896367110327</v>
+        <v>0.1738988455985447</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.009440942066222488</v>
+        <v>0.00125984885982593</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.298037343944809</v>
+        <v>0.1737704805314271</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0039303844252945</v>
+        <v>0.0005216478520764742</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.296445657029138</v>
+        <v>0.1735530325628943</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002722087045752315</v>
+        <v>0.0003600006147823557</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.297956655837964</v>
+        <v>0.1737511243069854</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001133455170814947</v>
+        <v>0.0001476960246084563</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>5.653970270522432</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.297498387069153</v>
+        <v>0.173685346450835</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0005856637042187651</v>
+        <v>7.384425011064962e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>5.653970270522432</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.297534427868099</v>
+        <v>0.1736858486608104</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002269899262110028</v>
+        <v>2.596698110056371e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.06608343730067917</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.297402048971632</v>
+        <v>0.1736637021157446</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001215519507552314</v>
+        <v>1.217899784007667e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.06608343730067917</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.297417904209835</v>
+        <v>0.173661533143555</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>5.711389054071077e-05</v>
+        <v>3.470075982824195e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.29741100224076</v>
+        <v>0.173656274871103</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.430540885788129e-05</v>
+        <v>-1.270220690815108e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.297402395000589</v>
+        <v>0.1736507879414423</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>7.912811891542016e-06</v>
+        <v>-3.155312586922569e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.297393345323467</v>
+        <v>0.1736452094161394</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>7.876374973718185e-07</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.297386990860328</v>
+        <v>0.1736400159214053</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-2.774949699713269e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.29738064486031</v>
+        <v>0.1736348236356883</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.29737469384955</v>
+        <v>0.1736346881270825</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.555348042317843e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.297369851542107</v>
+        <v>0.1736347279825548</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.297364930340559</v>
+        <v>0.1736347678380271</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.297364922369465</v>
+        <v>0.1736347598669326</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.297365081791354</v>
+        <v>0.1736349192888217</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>5.653970270522432</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.29736498613822</v>
+        <v>0.1736348236356883</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.06608343730067917</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.297365336866377</v>
+        <v>0.1736351743638446</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.06608343730067917</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.297365089762448</v>
+        <v>0.1736349272599162</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.297365049906976</v>
+        <v>0.1736348874044439</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.29736498613822</v>
+        <v>0.1736348236356883</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.29736505787807</v>
+        <v>0.1736348953755384</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.29736498613822</v>
+        <v>0.1736348236356883</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>5.653970270522432</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.297365089762448</v>
+        <v>0.1736349272599162</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.06608343730067917</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.297365185415582</v>
+        <v>0.1736350229130499</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.06608343730067917</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.297365121646826</v>
+        <v>0.173634959144294</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.297365081791354</v>
+        <v>0.1736349192888217</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.29736505787807</v>
+        <v>0.1736348953755384</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.297364810774142</v>
+        <v>0.1736346482716103</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.297364731063198</v>
+        <v>0.1736345685606655</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.297364778889765</v>
+        <v>0.1736346163872322</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.297364898456181</v>
+        <v>0.1736347359536493</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.297364882513993</v>
+        <v>0.1736347200114604</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.297364898456181</v>
+        <v>0.1736347359536493</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.297364882513993</v>
+        <v>0.1736347200114604</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.297364938311654</v>
+        <v>0.1736347758091215</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.297364938311654</v>
+        <v>0.1736347758091215</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.297364938311654</v>
+        <v>0.1736347758091215</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.297365089762448</v>
+        <v>0.1736349272599162</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.297365304981999</v>
+        <v>0.1736351424794667</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.29736521729996</v>
+        <v>0.1736350547974277</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.297365169473393</v>
+        <v>0.173635006970861</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.29736521729996</v>
+        <v>0.1736350547974277</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.297365033964787</v>
+        <v>0.173634871462255</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.297365041935882</v>
+        <v>0.1736348794333495</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.297365049906976</v>
+        <v>0.1736348874044439</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.29736505787807</v>
+        <v>0.1736348953755384</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.29736505787807</v>
+        <v>0.1736348953755384</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.297365097733543</v>
+        <v>0.1736349352310107</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.297365161502299</v>
+        <v>0.1736349989997665</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.297365273097621</v>
+        <v>0.1736351105950889</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.297365320924188</v>
+        <v>0.1736351584216556</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.297365281068715</v>
+        <v>0.1736351185661834</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.297365209328865</v>
+        <v>0.1736350468263333</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.297365328895282</v>
+        <v>0.1736351663927501</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.297365169473393</v>
+        <v>0.173635006970861</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.297364938311654</v>
+        <v>0.1736347758091215</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.297364890485087</v>
+        <v>0.1736347279825548</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.297364922369465</v>
+        <v>0.1736347598669326</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.29736498613822</v>
+        <v>0.1736348236356883</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.29736498613822</v>
+        <v>0.1736348236356883</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.297364906427276</v>
+        <v>0.1736347439247437</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.297364786860859</v>
+        <v>0.1736346243583267</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.297364747005387</v>
+        <v>0.1736345845028544</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.297364890485087</v>
+        <v>0.1736347279825548</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.297365025993693</v>
+        <v>0.1736348634911606</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.297365010051504</v>
+        <v>0.1736348475489717</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.29736498613822</v>
+        <v>0.1736348236356883</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.297364946282748</v>
+        <v>0.173634783780216</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.29736484265852</v>
+        <v>0.1736346801559881</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.297364723092103</v>
+        <v>0.173634560589571</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.29736484265852</v>
+        <v>0.1736346801559881</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.297364890485087</v>
+        <v>0.1736347279825548</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.29736498613822</v>
+        <v>0.1736348236356883</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.297364866571804</v>
+        <v>0.1736347040692715</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.297364874542898</v>
+        <v>0.1736347120403659</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_2_000001.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.6660834373006792</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>5.653970270522432</v>
+        <v>1.996323785759845</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>5.653970270522432</v>
+        <v>3.04</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>5.653970270522432</v>
+        <v>3.04</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0004499998998588417</v>
+        <v>-0.0003482931056141388</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1937568916215206</v>
+        <v>0.1499647918905749</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>5.653970270522432</v>
+        <v>1.996323785759845</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.3880308691591267</v>
+        <v>0.3003300151321755</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.7485845139206162</v>
+        <v>0.5793941278198403</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.06608343730067917</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.69194014772856</v>
+        <v>1.309536763645926</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2302687928309839</v>
+        <v>0.1782243726220535</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.402944936957548</v>
+        <v>1.085858936158785</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.04672325095406269</v>
+        <v>0.03616325751807207</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.265761806680401</v>
+        <v>0.9796812439342251</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.04046441184238865</v>
+        <v>0.03131863042204541</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.29991602913028</v>
+        <v>1.006115984780039</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01978213259579021</v>
+        <v>0.01531131745512743</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.29896367110327</v>
+        <v>1.005378874566266</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.009440942066222488</v>
+        <v>0.007306133768734984</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.298037343944809</v>
+        <v>1.00466079450055</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0039303844252945</v>
+        <v>0.003040761520835508</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.296445657029138</v>
+        <v>1.003427789957385</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002722087045752315</v>
+        <v>0.002105521525221444</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6660834373006792</v>
+        <v>0.7526475715196894</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.297956655837964</v>
+        <v>1.004596086138075</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001133455170814947</v>
+        <v>0.0008763846483728617</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>5.653970270522432</v>
+        <v>1.996323785759845</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.297498387069153</v>
+        <v>1.004240267120295</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0005856637042187651</v>
+        <v>0.0004520293819973249</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>5.653970270522432</v>
+        <v>1.996323785759845</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.297534427868099</v>
+        <v>1.004267022670611</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002269899262110028</v>
+        <v>0.0001745035175659795</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.06608343730067917</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.297402048971632</v>
+        <v>1.004163462529</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001215519507552314</v>
+        <v>9.2920287688437e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.06608343730067917</v>
+        <v>-0.09102864272046568</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.297417904209835</v>
+        <v>1.004174599387519</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>5.711389054071077e-05</v>
+        <v>4.299709723600378e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.29741100224076</v>
+        <v>1.004168127872531</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.430540885788129e-05</v>
+        <v>1.791150147070719e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.297402395000589</v>
+        <v>1.004160332594365</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>7.912811891542016e-06</v>
+        <v>4.684608918656512e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.297393345323467</v>
+        <v>1.004152223596674</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>7.876374973718185e-07</v>
+        <v>-4.525705377792857e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.297386990860328</v>
+        <v>1.004146159375635</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-2.774949699713269e-06</v>
+        <v>-3.410678356938051e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.29738064486031</v>
+        <v>1.004140102293917</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.29737469384955</v>
+        <v>1.004134286791764</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.555348042317843e-06</v>
+        <v>-4.777674021158921e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.297369851542107</v>
+        <v>1.004129405493514</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.297364930340559</v>
+        <v>1.004124484291967</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.297364922369465</v>
+        <v>1.004124476320872</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6660834373006792</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.297365081791354</v>
+        <v>1.004124635742761</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>5.653970270522432</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.29736498613822</v>
+        <v>1.004124540089628</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.06608343730067917</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.297365336866377</v>
+        <v>1.004124890817784</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.06608343730067917</v>
+        <v>-0.09102864272046568</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.297365089762448</v>
+        <v>1.004124643713856</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.09102864272046568</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.297365049906976</v>
+        <v>1.004124603858383</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.29736498613822</v>
+        <v>1.004124540089628</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.29736505787807</v>
+        <v>1.004124611829478</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6660834373006792</v>
+        <v>0.7526475715196894</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.29736498613822</v>
+        <v>1.004124540089628</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>5.653970270522432</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.297365089762448</v>
+        <v>1.004124643713856</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.06608343730067917</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.297365185415582</v>
+        <v>1.004124739366989</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.06608343730067917</v>
+        <v>-0.09102864272046568</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.297365121646826</v>
+        <v>1.004124675598233</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.297365081791354</v>
+        <v>1.004124635742761</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.29736505787807</v>
+        <v>1.004124611829478</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.297364810774142</v>
+        <v>1.00412436472555</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.297364731063198</v>
+        <v>1.004124285014605</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.297364778889765</v>
+        <v>1.004124332841172</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.297364898456181</v>
+        <v>1.004124452407589</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.297364882513993</v>
+        <v>1.0041244364654</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.297364898456181</v>
+        <v>1.004124452407589</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.297364882513993</v>
+        <v>1.0041244364654</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.297364938311654</v>
+        <v>1.004124492263061</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.297364938311654</v>
+        <v>1.004124492263061</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.297364938311654</v>
+        <v>1.004124492263061</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.297365089762448</v>
+        <v>1.004124643713856</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.297365304981999</v>
+        <v>1.004124858933406</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.29736521729996</v>
+        <v>1.004124771251367</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.297365169473393</v>
+        <v>1.004124723424801</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.29736521729996</v>
+        <v>1.004124771251367</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.297365033964787</v>
+        <v>1.004124587916194</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.297365041935882</v>
+        <v>1.004124595887289</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.297365049906976</v>
+        <v>1.004124603858383</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.29736505787807</v>
+        <v>1.004124611829478</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.29736505787807</v>
+        <v>1.004124611829478</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.297365097733543</v>
+        <v>1.00412465168495</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.297365161502299</v>
+        <v>1.004124715453706</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.297365273097621</v>
+        <v>1.004124827049028</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.297365320924188</v>
+        <v>1.004124874875595</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.297365281068715</v>
+        <v>1.004124835020123</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.297365209328865</v>
+        <v>1.004124763280273</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.297365328895282</v>
+        <v>1.00412488284669</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.297365169473393</v>
+        <v>1.004124723424801</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.297364938311654</v>
+        <v>1.004124492263061</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.297364890485087</v>
+        <v>1.004124444436494</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.297364922369465</v>
+        <v>1.004124476320872</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.29736498613822</v>
+        <v>1.004124540089628</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.29736498613822</v>
+        <v>1.004124540089628</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.297364906427276</v>
+        <v>1.004124460378683</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.297364786860859</v>
+        <v>1.004124340812266</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.297364747005387</v>
+        <v>1.004124300956794</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.297364890485087</v>
+        <v>1.004124444436494</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.297365025993693</v>
+        <v>1.0041245799451</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.297365010051504</v>
+        <v>1.004124564002911</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.29736498613822</v>
+        <v>1.004124540089628</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.297364946282748</v>
+        <v>1.004124500234155</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.29736484265852</v>
+        <v>1.004124396609928</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.297364723092103</v>
+        <v>1.00412427704351</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.29736484265852</v>
+        <v>1.004124396609928</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.297364890485087</v>
+        <v>1.004124444436494</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.29736498613822</v>
+        <v>1.004124540089628</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.297364866571804</v>
+        <v>1.004124420523211</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204657</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.297364874542898</v>
+        <v>1.004124428494305</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_2_000001.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.009757671505212784</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.005600340664386749</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.00841696560382843</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.009721994400024414</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.00812298059463501</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.004668861627578735</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.01033568382263184</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.01040404662489891</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.008390758186578751</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.01099231094121933</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.009107340127229691</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.01020446419715881</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.00775502622127533</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.004180680960416794</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.002601999789476395</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.002020031213760376</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.005021825432777405</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.004465542733669281</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.004600174725055695</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.006411980837583542</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.006456717848777771</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.005267694592475891</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.00409490242600441</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.003873664885759354</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.005662444978952408</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.006020646542310715</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.006400618702173233</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.007767349481582642</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.006093189120292664</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.002522282302379608</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.006998147815465927</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.005671039223670959</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.008165944367647171</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.008572153747081757</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.008934330195188522</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.007730334997177124</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.006893325597047806</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.006056278944015503</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.002014778554439545</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.0004839003086090088</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.996323785759845</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.004161596298217773</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.04</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.004680175334215164</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.04</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0003482931056141388</v>
+        <v>-0.0001816752822221024</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1499647918905749</v>
+        <v>0.07822410178061202</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.005216855555772781</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.996323785759845</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.3003300151321755</v>
+        <v>0.1566569630070983</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5793941278198403</v>
+        <v>0.3022210742498265</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.0009648129343986511</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.309536763645926</v>
+        <v>0.6830750487817598</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1782243726220535</v>
+        <v>0.09296489660347235</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.002709601074457169</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.085858936158785</v>
+        <v>0.5664011813620098</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03616325751807207</v>
+        <v>0.01886306248949166</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.0007191374897956848</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.16</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.9796812439342251</v>
+        <v>0.5110173888417329</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03131863042204541</v>
+        <v>0.01633660823303623</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.00296049565076828</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.006115984780039</v>
+        <v>0.5248062758631562</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01531131745512743</v>
+        <v>0.007985702361668543</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.0004494227468967438</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.16</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.005378874566266</v>
+        <v>0.524420894243811</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.007306133768734984</v>
+        <v>0.003808255384588791</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.00134708359837532</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.16</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.00466079450055</v>
+        <v>0.5240439424238605</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003040761520835508</v>
+        <v>0.001583850919478074</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.0011940598487854</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.003427789957385</v>
+        <v>0.5233983419913631</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002105521525221444</v>
+        <v>0.001096175216267276</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.002342574298381805</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.7526475715196894</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.004596086138075</v>
+        <v>0.5240054028804111</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0008763846483728617</v>
+        <v>0.0004543766478726977</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.001184262335300446</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.996323785759845</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.004240267120295</v>
+        <v>0.5238174288811471</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004520293819973249</v>
+        <v>0.0002335372651652704</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.0008315928280353546</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.996323785759845</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.004267022670611</v>
+        <v>0.5238290030499527</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001745035175659795</v>
+        <v>8.842580738814138e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.002511732280254364</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.004163462529</v>
+        <v>0.5237725621866074</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.2920287688437e-05</v>
+        <v>4.596436025889411e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.002634298056364059</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.09102864272046568</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.004174599387519</v>
+        <v>0.5237760087290115</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.299709723600378e-05</v>
+        <v>2.041022794847258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.004798334091901779</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.004168127872531</v>
+        <v>0.5237702339116556</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.791150147070719e-05</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.003898054361343384</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.004160332594365</v>
+        <v>0.5237637718849604</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.684608918656512e-06</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.003749009221792221</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.004152223596674</v>
+        <v>0.5237571092005268</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.525705377792857e-07</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.003496386110782623</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.004146159375635</v>
+        <v>0.5237515287163241</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.410678356938051e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.002485319972038269</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.004140102293917</v>
+        <v>0.5237459518591734</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.00338204950094223</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.004134286791764</v>
+        <v>0.5237405445165164</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.002050209790468216</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.004129405493514</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.003840643912553787</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.16</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.004124484291967</v>
+        <v>0.5237356632182673</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.001701325178146362</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.004124476320872</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.002814322710037231</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.16</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.004124635742761</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.0001756735146045685</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.004124540089628</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.001884572207927704</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.9526475715196895</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.004124890817784</v>
+        <v>0.5237360697440847</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.002826165407896042</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.09102864272046568</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.004124643713856</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.002133086323738098</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.09102864272046568</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.004124603858383</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.004131149500608444</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.004124540089628</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.003718636929988861</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.004124611829478</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.003541722893714905</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.7526475715196894</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.004124540089628</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.004562202841043472</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.004124643713856</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.001492641866207123</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.004124739366989</v>
+        <v>0.52373591829329</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.003315918147563934</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.09102864272046568</v>
+        <v>0.16</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.004124675598233</v>
+        <v>0.5237358545245342</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.004565276205539703</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.004124635742761</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.002416267991065979</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.004124611829478</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.003966290503740311</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.00412436472555</v>
+        <v>0.5237355436518504</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.004939001053571701</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.004124285014605</v>
+        <v>0.5237354639409056</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.004691816866397858</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.004124332841172</v>
+        <v>0.5237355117674724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.005257446318864822</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.004124452407589</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.004230771213769913</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.0041244364654</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.004492610692977905</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.004124452407589</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.004072792828083038</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.0041244364654</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.00437086820602417</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.004124492263061</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.005355048924684525</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.004124492263061</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.001991946250200272</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.004124492263061</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.004581071436405182</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.004124643713856</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.0007288902997970581</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.004124858933406</v>
+        <v>0.5237360378597069</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.004816319793462753</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.004124771251367</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.004351746290922165</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.004124723424801</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.003630515187978745</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.004124771251367</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.005027998238801956</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.004124587916194</v>
+        <v>0.5237357668424952</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.004955455660820007</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.004124595887289</v>
+        <v>0.5237357748135897</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.004352536052465439</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.004124603858383</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.005334407091140747</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.004124611829478</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.005192548036575317</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.004124611829478</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.002465736120939255</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.00412465168495</v>
+        <v>0.5237358306112508</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.003597870469093323</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.004124715453706</v>
+        <v>0.5237358943800067</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.00313270092010498</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.004124827049028</v>
+        <v>0.5237360059753291</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.004553060978651047</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.004124874875595</v>
+        <v>0.5237360538018958</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.00371880829334259</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.004124835020123</v>
+        <v>0.5237360139464236</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.003684893250465393</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.004124763280273</v>
+        <v>0.5237359422065735</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.003305163234472275</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.00412488284669</v>
+        <v>0.5237360617729903</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.002524815499782562</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.004124723424801</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.004073716700077057</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.004124492263061</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.004095710813999176</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.3</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.004124444436494</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.004971873015165329</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.004124476320872</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.004130184650421143</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.004124540089628</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.005074534565210342</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.004124540089628</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.004931386560201645</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.004124460378683</v>
+        <v>0.5237356393049839</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.004599764943122864</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.004124340812266</v>
+        <v>0.5237355197385668</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.004888016730546951</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.004124300956794</v>
+        <v>0.5237354798830945</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.004234857857227325</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.004124444436494</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.004721608012914658</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.0041245799451</v>
+        <v>0.5237357588714008</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.005197886377573013</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.004124564002911</v>
+        <v>0.5237357429292118</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.004810888320207596</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.004124540089628</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.00466855987906456</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.004124500234155</v>
+        <v>0.5237356791604562</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.003533490002155304</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.004124396609928</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003162793815135956</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.00412427704351</v>
+        <v>0.5237354559698112</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.004507947713136673</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.004124396609928</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.003924965858459473</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.004124444436494</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.004777520895004272</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.004124540089628</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.004503238946199417</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.2910286427204657</v>
+        <v>0.02000000000000013</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.004124420523211</v>
+        <v>0.5237355994495116</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.003454480320215225</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.2910286427204657</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.004124428494305</v>
+        <v>0.5237356074206061</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_2_000001.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000001.xlsx
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.00841696560382843</v>
+        <v>-0.008416973054409027</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.009721994400024414</v>
+        <v>-0.009721998125314713</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.00812298059463501</v>
+        <v>-0.008122999221086502</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.004668861627578735</v>
+        <v>-0.004668839275836945</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.01033568382263184</v>
+        <v>-0.01033569499850273</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.01040404662489891</v>
+        <v>-0.01040402427315712</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.01099231094121933</v>
+        <v>-0.01099231839179993</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.009107340127229691</v>
+        <v>-0.009107332676649094</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.01020446419715881</v>
+        <v>-0.01020443439483643</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.2599999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.00775502622127533</v>
+        <v>-0.007755011320114136</v>
       </c>
       <c r="JB14" t="n">
         <v>0.02000000000000007</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.004180680960416794</v>
+        <v>-0.004180695861577988</v>
       </c>
       <c r="JB15" t="n">
         <v>0.3</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.002020031213760376</v>
+        <v>-0.002020016312599182</v>
       </c>
       <c r="JB17" t="n">
         <v>0.8599999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.005021825432777405</v>
+        <v>-0.005021803081035614</v>
       </c>
       <c r="JB18" t="n">
         <v>0.8599999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.004465542733669281</v>
+        <v>-0.004465524107217789</v>
       </c>
       <c r="JB19" t="n">
         <v>0.7199999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.004600174725055695</v>
+        <v>-0.004600152373313904</v>
       </c>
       <c r="JB20" t="n">
         <v>0.5799999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.006411980837583542</v>
+        <v>-0.006411988288164139</v>
       </c>
       <c r="JB21" t="n">
         <v>0.4399999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.006456717848777771</v>
+        <v>-0.006456725299358368</v>
       </c>
       <c r="JB22" t="n">
         <v>0.4399999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.005267694592475891</v>
+        <v>-0.005267675966024399</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.02000000000000007</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.00409490242600441</v>
+        <v>-0.004094909876585007</v>
       </c>
       <c r="JB24" t="n">
         <v>0.1199999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.003873664885759354</v>
+        <v>-0.003873672336339951</v>
       </c>
       <c r="JB25" t="n">
         <v>0.8599999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.005662444978952408</v>
+        <v>-0.005662448704242706</v>
       </c>
       <c r="JB26" t="n">
         <v>0.8599999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.006400618702173233</v>
+        <v>-0.006400641053915024</v>
       </c>
       <c r="JB28" t="n">
         <v>0.4399999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.007767349481582642</v>
+        <v>-0.00776735320687294</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.1600000000000001</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.006093189120292664</v>
+        <v>-0.006093177944421768</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.4399999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.002522282302379608</v>
+        <v>-0.002522263675928116</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.006998147815465927</v>
+        <v>-0.00699814036488533</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.3</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.005671039223670959</v>
+        <v>-0.005671024322509766</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.008165944367647171</v>
+        <v>-0.008165962994098663</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.7199999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.008572153747081757</v>
+        <v>-0.008572135120630264</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.7199999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.008934330195188522</v>
+        <v>-0.008934322744607925</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.9999999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.007730334997177124</v>
+        <v>-0.00773032009601593</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.006893325597047806</v>
+        <v>-0.00689331442117691</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.4399999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.006056278944015503</v>
+        <v>-0.006056275218725204</v>
       </c>
       <c r="JB39" t="n">
         <v>0.4399999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.002014778554439545</v>
+        <v>-0.002014771103858948</v>
       </c>
       <c r="JB40" t="n">
         <v>0.7199999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.0004839003086090088</v>
+        <v>0.0004838891327381134</v>
       </c>
       <c r="JB41" t="n">
         <v>0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.004161596298217773</v>
+        <v>0.00416160374879837</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.004680175334215164</v>
+        <v>0.004680179059505463</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.005216855555772781</v>
+        <v>0.005216825753450394</v>
       </c>
       <c r="JB44" t="n">
         <v>0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.0009648129343986511</v>
+        <v>-0.0009647980332374573</v>
       </c>
       <c r="JB45" t="n">
         <v>0.7199999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.002709601074457169</v>
+        <v>-0.002709578722715378</v>
       </c>
       <c r="JB46" t="n">
         <v>0.5799999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.0007191374897956848</v>
+        <v>-0.000719171017408371</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.16</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.00296049565076828</v>
+        <v>-0.002960484474897385</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.3</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.0004494227468967438</v>
+        <v>-0.0004493966698646545</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.16</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.00134708359837532</v>
+        <v>-0.001347087323665619</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.16</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.0011940598487854</v>
+        <v>-0.001194082200527191</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.02000000000000007</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.002342574298381805</v>
+        <v>-0.002342600375413895</v>
       </c>
       <c r="JB52" t="n">
         <v>0.1199999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.001184262335300446</v>
+        <v>0.00118425115942955</v>
       </c>
       <c r="JB53" t="n">
         <v>0.7199999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.0008315928280353546</v>
+        <v>0.0008315816521644592</v>
       </c>
       <c r="JB54" t="n">
         <v>0.5799999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.002511732280254364</v>
+        <v>-0.002511724829673767</v>
       </c>
       <c r="JB55" t="n">
         <v>0.4399999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.004798334091901779</v>
+        <v>-0.004798326641321182</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.7199999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.003898054361343384</v>
+        <v>-0.003898084163665771</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.8599999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.003749009221792221</v>
+        <v>-0.003749024122953415</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.7199999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.003496386110782623</v>
+        <v>-0.003496378660202026</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.7199999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.002485319972038269</v>
+        <v>-0.002485323697328568</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.4399999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.002050209790468216</v>
+        <v>-0.002050183713436127</v>
       </c>
       <c r="JB63" t="n">
         <v>0.4399999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.003840643912553787</v>
+        <v>-0.003840647637844086</v>
       </c>
       <c r="JB64" t="n">
         <v>0.16</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.001701325178146362</v>
+        <v>-0.001701317727565765</v>
       </c>
       <c r="JB65" t="n">
         <v>0.4399999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.0001756735146045685</v>
+        <v>0.0001756325364112854</v>
       </c>
       <c r="JB67" t="n">
         <v>0.1600000000000001</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.001884572207927704</v>
+        <v>-0.001884568482637405</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.7199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.002826165407896042</v>
+        <v>-0.002826176583766937</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.7199999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.002133086323738098</v>
+        <v>-0.002133090049028397</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.004131149500608444</v>
+        <v>-0.004131127148866653</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.003718636929988861</v>
+        <v>-0.00371864065527916</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.7199999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.003541722893714905</v>
+        <v>-0.003541719168424606</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.4399999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.004562202841043472</v>
+        <v>0.004562228918075562</v>
       </c>
       <c r="JB74" t="n">
         <v>0.1600000000000001</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.001492641866207123</v>
+        <v>-0.001492653042078018</v>
       </c>
       <c r="JB75" t="n">
         <v>0.1600000000000001</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.003315918147563934</v>
+        <v>-0.003315936774015427</v>
       </c>
       <c r="JB76" t="n">
         <v>0.16</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.004565276205539703</v>
+        <v>-0.0045652836561203</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.1199999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.002416267991065979</v>
+        <v>-0.002416279166936874</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.003966290503740311</v>
+        <v>-0.003966331481933594</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.004939001053571701</v>
+        <v>-0.004938971251249313</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.004691816866397858</v>
+        <v>-0.004691809415817261</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.005257446318864822</v>
+        <v>-0.005257450044155121</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.004230771213769913</v>
+        <v>-0.004230823367834091</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.9999999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.004492610692977905</v>
+        <v>-0.004492618143558502</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.9999999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.004072792828083038</v>
+        <v>-0.004072844982147217</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.9999999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.00437086820602417</v>
+        <v>-0.004370924085378647</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.1199999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.001991946250200272</v>
+        <v>-0.001991938799619675</v>
       </c>
       <c r="JB88" t="n">
         <v>0.1600000000000001</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.004581071436405182</v>
+        <v>-0.004581063985824585</v>
       </c>
       <c r="JB89" t="n">
         <v>0.16</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.0007288902997970581</v>
+        <v>-0.0007288679480552673</v>
       </c>
       <c r="JB90" t="n">
         <v>0.1600000000000001</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.004816319793462753</v>
+        <v>-0.004816312342882156</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.1199999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.004351746290922165</v>
+        <v>-0.004351727664470673</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.1199999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.003630515187978745</v>
+        <v>-0.003630541265010834</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.9999999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.005027998238801956</v>
+        <v>-0.005027990788221359</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.9999999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.004955455660820007</v>
+        <v>-0.004955478012561798</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.9999999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.004352536052465439</v>
+        <v>-0.004352517426013947</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.9999999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.005334407091140747</v>
+        <v>-0.005334410816431046</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.7199999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.005192548036575317</v>
+        <v>-0.005192581564188004</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.5799999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.002465736120939255</v>
+        <v>-0.002465751022100449</v>
       </c>
       <c r="JB99" t="n">
         <v>0.3</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.003597870469093323</v>
+        <v>-0.003597840666770935</v>
       </c>
       <c r="JB100" t="n">
         <v>0.3</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.00313270092010498</v>
+        <v>-0.003132704645395279</v>
       </c>
       <c r="JB101" t="n">
         <v>0.4399999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.004553060978651047</v>
+        <v>-0.004553049802780151</v>
       </c>
       <c r="JB102" t="n">
         <v>0.3</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.003684893250465393</v>
+        <v>-0.003684896975755692</v>
       </c>
       <c r="JB104" t="n">
         <v>0.4399999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.003305163234472275</v>
+        <v>-0.003305178135633469</v>
       </c>
       <c r="JB105" t="n">
         <v>0.5799999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.002524815499782562</v>
+        <v>-0.002524793148040771</v>
       </c>
       <c r="JB106" t="n">
         <v>0.5799999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.004073716700077057</v>
+        <v>-0.004073735326528549</v>
       </c>
       <c r="JB107" t="n">
         <v>0.4399999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.004095710813999176</v>
+        <v>-0.004095718264579773</v>
       </c>
       <c r="JB108" t="n">
         <v>0.3</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.004971873015165329</v>
+        <v>-0.004971858114004135</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.5799999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.004130184650421143</v>
+        <v>-0.004130199551582336</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.7199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.005074534565210342</v>
+        <v>-0.005074508488178253</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.8599999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.004931386560201645</v>
+        <v>-0.004931356757879257</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.8599999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.004599764943122864</v>
+        <v>-0.004599776118993759</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.004234857857227325</v>
+        <v>-0.004234861582517624</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.9999999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.004721608012914658</v>
+        <v>-0.004721619188785553</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.9999999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.005197886377573013</v>
+        <v>-0.005197908729314804</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.9999999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.004810888320207596</v>
+        <v>-0.004810880869626999</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.7199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.00466855987906456</v>
+        <v>-0.004668530076742172</v>
       </c>
       <c r="JB119" t="n">
         <v>0.16</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.003533490002155304</v>
+        <v>-0.003533493727445602</v>
       </c>
       <c r="JB120" t="n">
         <v>0.1600000000000001</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.003162793815135956</v>
+        <v>-0.003162804991006851</v>
       </c>
       <c r="JB121" t="n">
         <v>0.4399999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.003924965858459473</v>
+        <v>-0.00392497330904007</v>
       </c>
       <c r="JB123" t="n">
         <v>0.1600000000000001</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.004777520895004272</v>
+        <v>-0.004777543246746063</v>
       </c>
       <c r="JB124" t="n">
         <v>0.02000000000000007</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.004503238946199417</v>
+        <v>-0.004503265023231506</v>
       </c>
       <c r="JB125" t="n">
         <v>0.02000000000000013</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.003454480320215225</v>
+        <v>-0.003454454243183136</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.5799999999999998</v>
